--- a/output/graficos_regionales/plot_regional_serie_i_ingr_m_2020_la_araucania.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_m_2020_la_araucania.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:38</t>
+    <t xml:space="preserve">2026-10-05 01:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -726,7 +726,7 @@
         <v>632805.25</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>804762.62</v>
+        <v>804762.63</v>
       </c>
     </row>
     <row r="5">
@@ -737,7 +737,7 @@
         <v>638500.81</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>799364.12</v>
+        <v>799364.13</v>
       </c>
     </row>
     <row r="6">
@@ -767,7 +767,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>639447.12</v>
+        <v>639447.13</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>805474.38</v>
@@ -778,7 +778,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>638348.62</v>
+        <v>638348.63</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>803301.44</v>
@@ -833,10 +833,10 @@
         <v>15</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>643371.62</v>
+        <v>643371.63</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>826816.62</v>
+        <v>826816.63</v>
       </c>
     </row>
     <row r="15">
@@ -855,7 +855,7 @@
         <v>17</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>673587.12</v>
+        <v>673587.13</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>844828.88</v>
@@ -913,7 +913,7 @@
         <v>683189.75</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>849932.62</v>
+        <v>849932.63</v>
       </c>
     </row>
     <row r="22">
@@ -1001,7 +1001,7 @@
         <v>711620.56</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>885489.12</v>
+        <v>885489.13</v>
       </c>
     </row>
     <row r="30">
@@ -1009,10 +1009,10 @@
         <v>31</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>709804.12</v>
+        <v>709804.13</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>873830.12</v>
+        <v>873830.13</v>
       </c>
     </row>
     <row r="31">
@@ -1031,7 +1031,7 @@
         <v>33</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>729051.62</v>
+        <v>729051.63</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>883003.31</v>
@@ -1152,7 +1152,7 @@
         <v>44</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>779428.12</v>
+        <v>779428.13</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>943650.75</v>
@@ -1166,7 +1166,7 @@
         <v>782028.56</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>953641.12</v>
+        <v>953641.13</v>
       </c>
     </row>
     <row r="45">
@@ -1207,7 +1207,7 @@
         <v>49</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>785270.12</v>
+        <v>785270.13</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>964866.69</v>
@@ -1273,7 +1273,7 @@
         <v>55</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>845562.12</v>
+        <v>845562.13</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>1035374.06</v>
@@ -1287,7 +1287,7 @@
         <v>856566.44</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>1048559.62</v>
+        <v>1048559.63</v>
       </c>
     </row>
     <row r="56">
@@ -1298,7 +1298,7 @@
         <v>858246.75</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1059287.62</v>
+        <v>1059287.63</v>
       </c>
     </row>
     <row r="57">
@@ -1342,7 +1342,7 @@
         <v>884925.06</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>1093564.62</v>
+        <v>1093564.63</v>
       </c>
     </row>
     <row r="61">
@@ -1364,7 +1364,7 @@
         <v>921485.88</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>1145616.62</v>
+        <v>1145616.63</v>
       </c>
     </row>
     <row r="63">
@@ -1372,7 +1372,7 @@
         <v>64</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>920843.62</v>
+        <v>920843.63</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>1133168.75</v>
@@ -1394,7 +1394,7 @@
         <v>66</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>959357.62</v>
+        <v>959357.63</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>1168289.25</v>
@@ -1419,7 +1419,7 @@
         <v>977017.94</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>1184430.62</v>
+        <v>1184430.63</v>
       </c>
     </row>
     <row r="68">
@@ -1518,7 +1518,7 @@
         <v>1003519.75</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>1240434.12</v>
+        <v>1240434.13</v>
       </c>
     </row>
     <row r="77">
@@ -1551,7 +1551,7 @@
         <v>1028468.19</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>1253268.12</v>
+        <v>1253268.13</v>
       </c>
     </row>
     <row r="80">
@@ -1562,7 +1562,7 @@
         <v>1042600.19</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>1274861.62</v>
+        <v>1274861.63</v>
       </c>
     </row>
     <row r="81">
@@ -1584,7 +1584,7 @@
         <v>1085996.88</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>1327655.12</v>
+        <v>1327655.13</v>
       </c>
     </row>
     <row r="83">
